--- a/MainTop/24.09.2026 Имена по 200/print200_p1.xlsx
+++ b/MainTop/24.09.2026 Имена по 200/print200_p1.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\24.09.2026 Имена по 200\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\24.09.2026 Имена по 200\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A818C11-8186-4EA8-B633-11E555D5AB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B798A1-7C8C-4915-91DD-75CE3202ACFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -571,6 +582,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -591,7 +605,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -605,7 +619,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -619,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -633,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -647,7 +661,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -661,7 +675,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -675,7 +689,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -689,7 +703,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -703,7 +717,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -717,7 +731,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -731,7 +745,7 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -745,7 +759,7 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -759,7 +773,7 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -773,7 +787,7 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -787,7 +801,7 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -801,7 +815,7 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -815,7 +829,7 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -829,7 +843,7 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -843,7 +857,7 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -857,7 +871,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -871,7 +885,7 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -885,7 +899,7 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -899,7 +913,7 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -913,7 +927,7 @@
         <v>29</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -927,7 +941,7 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -941,7 +955,7 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -955,7 +969,7 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -969,7 +983,7 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -983,7 +997,7 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -997,7 +1011,7 @@
         <v>35</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1011,7 +1025,7 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1025,7 +1039,7 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1039,7 +1053,7 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1053,7 +1067,7 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1067,7 +1081,7 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1081,7 +1095,7 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1095,7 +1109,7 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1109,7 +1123,7 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1123,7 +1137,7 @@
         <v>44</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1137,7 +1151,7 @@
         <v>45</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1151,7 +1165,7 @@
         <v>46</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1165,7 +1179,7 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1179,7 +1193,7 @@
         <v>48</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1193,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1207,7 +1221,7 @@
         <v>50</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1221,7 +1235,7 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1235,7 +1249,7 @@
         <v>52</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1249,7 +1263,7 @@
         <v>53</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1263,7 +1277,7 @@
         <v>54</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1277,7 +1291,7 @@
         <v>55</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1291,7 +1305,7 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1305,7 +1319,7 @@
         <v>57</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1319,7 +1333,7 @@
         <v>58</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1333,7 +1347,7 @@
         <v>59</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1347,7 +1361,7 @@
         <v>60</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -1361,7 +1375,7 @@
         <v>61</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -1375,7 +1389,7 @@
         <v>62</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1389,7 +1403,7 @@
         <v>63</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -1403,7 +1417,7 @@
         <v>64</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1417,7 +1431,7 @@
         <v>65</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1431,7 +1445,7 @@
         <v>66</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1445,7 +1459,7 @@
         <v>67</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1459,7 +1473,7 @@
         <v>68</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1473,7 +1487,7 @@
         <v>69</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
